--- a/src/main/resources/BTNBest - Claim Benefit.xlsx
+++ b/src/main/resources/BTNBest - Claim Benefit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KERJA\Intellij Project\Testing\Testing\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A451A6-3500-49C4-AB69-774589AD9527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E2E501-4C78-412C-94DD-1A1BEDA2D26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA-INFO" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="dt_Initial Data Entry" sheetId="6" state="hidden" r:id="rId3"/>
     <sheet name="LIMIT 1" sheetId="4" r:id="rId4"/>
     <sheet name="Data LIMIT 1" sheetId="9" r:id="rId5"/>
-    <sheet name="Xpath" sheetId="3" r:id="rId6"/>
+    <sheet name="Data_Attachment" sheetId="10" r:id="rId6"/>
+    <sheet name="XPATH" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="231">
   <si>
     <t>Start Data</t>
   </si>
@@ -67,9 +68,6 @@
     <t>Value</t>
   </si>
   <si>
-    <t>start_chrome_driver</t>
-  </si>
-  <si>
     <t>go_to_url</t>
   </si>
   <si>
@@ -91,9 +89,6 @@
     <t>SCENARIO</t>
   </si>
   <si>
-    <t>URL 2</t>
-  </si>
-  <si>
     <t>PASSWORD</t>
   </si>
   <si>
@@ -139,9 +134,6 @@
     <t>KETERANGAN</t>
   </si>
   <si>
-    <t>REGRESI</t>
-  </si>
-  <si>
     <t>LIMIT 1</t>
   </si>
   <si>
@@ -157,12 +149,6 @@
     <t>USERNAME</t>
   </si>
   <si>
-    <t>NIKI.NAKILA@TEST.COM</t>
-  </si>
-  <si>
-    <t>Btnbest123#</t>
-  </si>
-  <si>
     <t>txtUsername</t>
   </si>
   <si>
@@ -259,12 +245,6 @@
     <t>txtToDateItem</t>
   </si>
   <si>
-    <t>02-Feb-2026</t>
-  </si>
-  <si>
-    <t>03-Feb-2026</t>
-  </si>
-  <si>
     <t>FROM DATE CLAIM</t>
   </si>
   <si>
@@ -355,47 +335,413 @@
     <t>btnSavePopUp</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Pegawai</t>
+  </si>
+  <si>
+    <t>111111111</t>
+  </si>
+  <si>
+    <t>Gigi Berlobang</t>
+  </si>
+  <si>
+    <t>Anna Pekayon</t>
+  </si>
+  <si>
+    <t>reimburse</t>
+  </si>
+  <si>
+    <t>IDR</t>
+  </si>
+  <si>
+    <t>Reimburse Duitku</t>
+  </si>
+  <si>
+    <t>btnAddAttachment</t>
+  </si>
+  <si>
+    <t>btnAddNewDocument</t>
+  </si>
+  <si>
+    <t>txtDocumentType</t>
+  </si>
+  <si>
+    <t>for_data_by_sheet</t>
+  </si>
+  <si>
+    <t>Data_Attachment;#LoopAttachment</t>
+  </si>
+  <si>
+    <t>end_for_data</t>
+  </si>
+  <si>
+    <t>#LoopAttachment</t>
+  </si>
+  <si>
+    <t>DOCUMENT NUMBER</t>
+  </si>
+  <si>
+    <t>DOCUMENT TYPE</t>
+  </si>
+  <si>
+    <t>DOCUMENT EXPIRED DATE</t>
+  </si>
+  <si>
+    <t>ISSUED DATE</t>
+  </si>
+  <si>
+    <t>ISSUED BY</t>
+  </si>
+  <si>
+    <t>11-Feb-2026</t>
+  </si>
+  <si>
+    <t>FILE PATH ATTACH</t>
+  </si>
+  <si>
+    <t>ODY</t>
+  </si>
+  <si>
+    <t>txtDocumentNumber</t>
+  </si>
+  <si>
+    <t>btnDocumentType</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>Benefit : Kwitansi</t>
+  </si>
+  <si>
+    <t>Benefit : Medical Check Up</t>
+  </si>
+  <si>
+    <t>Benefit : Surat Keterangan Sakit</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>Kwitansi</t>
+  </si>
+  <si>
+    <t>MCU</t>
+  </si>
+  <si>
+    <t>Surat Keterangan Sakit</t>
+  </si>
+  <si>
+    <t>txtDocExpiredDate</t>
+  </si>
+  <si>
+    <t>txtDocumentDescription</t>
+  </si>
+  <si>
+    <t>txtDocIssuedDate</t>
+  </si>
+  <si>
+    <t>txtDocIssuedBy</t>
+  </si>
+  <si>
+    <t>txtUploadDocument</t>
+  </si>
+  <si>
+    <t>set_text_hidden</t>
+  </si>
+  <si>
+    <t>popUp_AlertBTNBEST</t>
+  </si>
+  <si>
+    <t>btnClosePopUp</t>
+  </si>
+  <si>
+    <t>btnValidation</t>
+  </si>
+  <si>
+    <t>btnSubmit</t>
+  </si>
+  <si>
+    <t>btnLogout</t>
+  </si>
+  <si>
+    <t>txtSearchMenu</t>
+  </si>
+  <si>
+    <t>wait_until_element_gone</t>
+  </si>
+  <si>
+    <t>imgProgressBar</t>
+  </si>
+  <si>
+    <t>Benefit Claim/Travel</t>
+  </si>
+  <si>
+    <t>Benefit Claim</t>
+  </si>
+  <si>
+    <t>if_element_exist_go_to_value</t>
+  </si>
+  <si>
+    <t>btnExpandEmployeeSelfService</t>
+  </si>
+  <si>
+    <t>#NEED EXPAND</t>
+  </si>
+  <si>
+    <t>anchor_go_to_value</t>
+  </si>
+  <si>
+    <t>#NEED EXPAND NOT EXIST</t>
+  </si>
+  <si>
+    <t>btnOKPopUp</t>
+  </si>
+  <si>
+    <t>C:\\KERJA\\UAT Script.docx</t>
+  </si>
+  <si>
+    <t>//input[@name='user_name']</t>
+  </si>
+  <si>
+    <t>//input[@name='password']</t>
+  </si>
+  <si>
+    <t>//a[contains(@class,'show-password')]</t>
+  </si>
+  <si>
+    <t>//button[@label='Login']</t>
+  </si>
+  <si>
+    <t>//div[contains(@class,'MuiAvatar')]</t>
+  </si>
+  <si>
+    <t>//*[local-name()='svg' and contains(@data-testid,'drawer')]</t>
+  </si>
+  <si>
+    <t>btnMenuItem</t>
+  </si>
+  <si>
+    <t>//li[@data-testid='menu-item']</t>
+  </si>
+  <si>
+    <t>//span[text()='Benefit Claim']</t>
+  </si>
+  <si>
+    <t>//a[text()='New']</t>
+  </si>
+  <si>
+    <t>//button[text()='Save']</t>
+  </si>
+  <si>
+    <t>//div[./div[@class='form-group'] and .//label[contains(text(),'Category')]]/following-sibling::div/button[./span[text()='search']]</t>
+  </si>
+  <si>
+    <t>//div[@role='presentation']//div[text()='Category']/following-sibling::div/input</t>
+  </si>
+  <si>
+    <t>(//span[text()='%'])[1]</t>
+  </si>
+  <si>
+    <t>//div[./div[@class='form-group'] and .//label[contains(text(),'Type')]]/following-sibling::div/button[./span[text()='search']]</t>
+  </si>
+  <si>
+    <t>//div[text()='Type']/following-sibling::div/input</t>
+  </si>
+  <si>
+    <t>//textarea[@name='purpose']</t>
+  </si>
+  <si>
+    <t>//label[contains(text(),'Claim Currency')]/following-sibling::div/div[@role='button']</t>
+  </si>
+  <si>
+    <t>//li[@data-value='%']</t>
+  </si>
+  <si>
+    <t>//textarea[@name='reference']</t>
+  </si>
+  <si>
+    <t>//textarea[@name='description']</t>
+  </si>
+  <si>
+    <t>//button[text()='New' and not(@disabled)]</t>
+  </si>
+  <si>
+    <t>//label[contains(text(),'From Date')]/following-sibling::div/input</t>
+  </si>
+  <si>
+    <t>//label[contains(text(),'To Date')]/following-sibling::div/input</t>
+  </si>
+  <si>
+    <t>//div[./div[@class='form-group'] and .//label[contains(text(),'Claim Item')]]/following-sibling::div/button[./span[text()='search']]</t>
+  </si>
+  <si>
+    <t>//div[text()='Claim Item']/following-sibling::div/input</t>
+  </si>
+  <si>
+    <t>//input[@name='claim_detail.quantity']</t>
+  </si>
+  <si>
+    <t>//label[contains(text(),'Amount/Unit')]/following-sibling::div/textarea[not(@aria-hidden='true')]</t>
+  </si>
+  <si>
+    <t>//label[contains(text(),'Adjusted Claim')]/following-sibling::div/textarea[not(@aria-hidden='true')]</t>
+  </si>
+  <si>
+    <t>//label[contains(text(),'Provider')]/following-sibling::div/textarea[not(@aria-hidden='true')]</t>
+  </si>
+  <si>
+    <t>//div[@role='presentation']//label[contains(text(),'Description')]/following-sibling::div/textarea[not(@aria-hidden='true')]</t>
+  </si>
+  <si>
+    <t>//div[./div[@class='form-group'] and .//label[contains(text(),'Relationship')]]/following-sibling::div/button[./span[text()='search']]</t>
+  </si>
+  <si>
+    <t>//div[text()='Relationship']/following-sibling::div/input</t>
+  </si>
+  <si>
+    <t>//div[text()='Contact Full Name']/following-sibling::div/input</t>
+  </si>
+  <si>
+    <t>//label[contains(text(),'Bill Number')]/following-sibling::div/textarea[not(@aria-hidden='true')]</t>
+  </si>
+  <si>
+    <t>//label[contains(text(),'Diagnosa')]/following-sibling::div/textarea[not(@aria-hidden='true')]</t>
+  </si>
+  <si>
+    <t>//div[text()='Value']/following-sibling::div/input</t>
+  </si>
+  <si>
+    <t>//label[contains(text(),'RS / Klinik Name')]/following-sibling::div/textarea[not(@aria-hidden='true')]</t>
+  </si>
+  <si>
+    <t>//div[@role='presentation']//button[text()='Save' and not(@disabled)]</t>
+  </si>
+  <si>
+    <t>//button[text()='Attachment' or text()='Lampiran']</t>
+  </si>
+  <si>
+    <t>//div[@role='presentation']//button[text()='New']</t>
+  </si>
+  <si>
+    <t>//textarea[@name='document_number']</t>
+  </si>
+  <si>
+    <t>//div[./div[@class='form-group'] and .//label[contains(text(),'Document Type')]]/following-sibling::div/button[./span[text()='search']]</t>
+  </si>
+  <si>
+    <t>//label[contains(text(),'Expired Date')]/following-sibling::div/input</t>
+  </si>
+  <si>
+    <t>//div[@role='presentation']//textarea[@name='description']</t>
+  </si>
+  <si>
+    <t>//label[contains(text(),'Issued Date')]/following-sibling::div/input</t>
+  </si>
+  <si>
+    <t>//textarea[@name='issued_by']</t>
+  </si>
+  <si>
+    <t>//input[@name='file_data']</t>
+  </si>
+  <si>
+    <t>//div[@role='presentation']/div[@role='alert']</t>
+  </si>
+  <si>
+    <t>//div[@role='presentation']//button[text()='Close']</t>
+  </si>
+  <si>
+    <t>//button[text()='Validation']</t>
+  </si>
+  <si>
+    <t>//button[text()='Submit']</t>
+  </si>
+  <si>
+    <t>//li[text()='Logout']</t>
+  </si>
+  <si>
+    <t>//div[@role='presentation']//button[text()='OK']</t>
+  </si>
+  <si>
+    <t>//div[./*[local-name()='svg' and @data-testid='SearchIcon']]/following-sibling::input</t>
+  </si>
+  <si>
+    <t>//span[@role='progressbar']</t>
+  </si>
+  <si>
+    <t>//li[@data-testid='menu-item' and ./div[span[text()='Employee Self Service']]]/*[local-name()='svg' and @data-testid='ExpandMoreIcon']</t>
+  </si>
+  <si>
+    <t>btnChooseFile</t>
+  </si>
+  <si>
+    <t>//label[@role='button' and text()='Choose File']</t>
+  </si>
+  <si>
+    <t>Logout</t>
+  </si>
+  <si>
+    <t>wait_for_seconds</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>lblLoadingInner</t>
+  </si>
+  <si>
+    <t>//div[contains(text(),'Loading')]</t>
+  </si>
+  <si>
+    <t>//div[./div[@class='form-group'] and .//label[contains(text(),'Nama') or contains(text(),'Name')]]/following-sibling::div/button[./span[text()='search']]</t>
+  </si>
+  <si>
+    <t>//div[./div[@class='form-group'] and .//label[contains(text(),'RS / Klinik') or contains(text(),'RS  / Klinik')]]/following-sibling::div/button[./span[text()='search']]</t>
+  </si>
+  <si>
+    <t>start_new_driver</t>
+  </si>
+  <si>
+    <t>DIDIT10131@TEST.COM</t>
+  </si>
+  <si>
+    <t>Btnbest321#</t>
+  </si>
+  <si>
     <t>Gigi</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>1000000</t>
-  </si>
-  <si>
     <t>Claim Gigi</t>
   </si>
   <si>
-    <t>Pegawai</t>
-  </si>
-  <si>
-    <t>NIKI NAKILA H</t>
-  </si>
-  <si>
-    <t>111111111</t>
-  </si>
-  <si>
-    <t>Gigi Berlobang</t>
-  </si>
-  <si>
-    <t>Anna Pekayon</t>
-  </si>
-  <si>
-    <t>reimburse</t>
-  </si>
-  <si>
-    <t>IDR</t>
-  </si>
-  <si>
-    <t>Reimburse Duitku</t>
+    <t>DIDIT NURYANTO</t>
+  </si>
+  <si>
+    <t>SIT</t>
+  </si>
+  <si>
+    <t>16-Jun-2026</t>
+  </si>
+  <si>
+    <t>6-Jun-2026</t>
+  </si>
+  <si>
+    <t>250000</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -426,8 +772,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -449,12 +801,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -495,11 +841,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -798,7 +1144,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -809,7 +1155,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -829,7 +1175,7 @@
     <col min="4" max="4" width="35.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.453125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.1796875" customWidth="1"/>
+    <col min="7" max="7" width="18" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.08984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
@@ -842,25 +1188,25 @@
         <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="G1" s="2" t="s">
-        <v>16</v>
+        <v>145</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -868,27 +1214,29 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
         <v>33</v>
       </c>
-      <c r="C2" t="s">
-        <v>36</v>
-      </c>
       <c r="D2" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2" s="7"/>
+        <v>32</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="G2" t="s">
+        <v>146</v>
+      </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="J9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -913,7 +1261,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -921,7 +1269,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -937,14 +1285,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.453125" customWidth="1"/>
     <col min="3" max="3" width="25.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="15.81640625" customWidth="1"/>
+    <col min="5" max="5" width="31.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.81640625" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.35">
@@ -952,7 +1301,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>5</v>
@@ -964,31 +1313,31 @@
         <v>7</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
-        <v>34</v>
+      <c r="F2" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
-        <v>8</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" t="str">
         <f>Datatable!$D$1</f>
@@ -997,49 +1346,52 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
-        <v>14</v>
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="str">
         <f>Datatable!$E$1</f>
         <v>USERNAME</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" t="str">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" t="str">
         <f>Datatable!$F$1</f>
         <v>PASSWORD</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-    </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C10" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -1047,196 +1399,201 @@
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" t="s">
-        <v>43</v>
+        <v>214</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C13" t="s">
-        <v>14</v>
+        <v>143</v>
+      </c>
+      <c r="D13" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4" t="s">
-        <v>34</v>
+      <c r="C14" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" t="s">
-        <v>44</v>
+      <c r="A15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C17" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>46</v>
+        <v>142</v>
+      </c>
+      <c r="E17" t="str">
+        <f>Datatable!$G$1</f>
+        <v>Benefit Claim/Travel</v>
       </c>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C18" t="s">
-        <v>14</v>
+        <v>47</v>
+      </c>
+      <c r="D18" t="s">
+        <v>142</v>
+      </c>
+      <c r="E18" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C19" t="s">
-        <v>20</v>
+        <v>143</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C20" t="s">
-        <v>22</v>
+        <v>147</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>148</v>
+      </c>
+      <c r="E20" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C21" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="D21" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="22" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C22" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" t="s">
-        <v>48</v>
+        <v>150</v>
+      </c>
+      <c r="E22" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C23" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C26" t="s">
         <v>18</v>
       </c>
-      <c r="D24" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" t="str">
+      <c r="D26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C29" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="str">
         <f>'Data LIMIT 1'!$B$1</f>
         <v>CATEGORY</v>
       </c>
     </row>
-    <row r="25" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C25" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C26" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C27" t="s">
-        <v>27</v>
-      </c>
-      <c r="D27" t="s">
-        <v>55</v>
-      </c>
-      <c r="E27" t="str">
+    <row r="32" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C32" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C33" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33" t="s">
+        <v>50</v>
+      </c>
+      <c r="E33" t="str">
         <f>'Data LIMIT 1'!$B$1</f>
         <v>CATEGORY</v>
-      </c>
-    </row>
-    <row r="28" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C28" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C29" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C30" t="s">
-        <v>18</v>
-      </c>
-      <c r="D30" t="s">
-        <v>57</v>
-      </c>
-      <c r="E30" t="str">
-        <f>'Data LIMIT 1'!$C$1</f>
-        <v>TYPE</v>
-      </c>
-    </row>
-    <row r="31" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C31" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31" t="s">
-        <v>57</v>
-      </c>
-      <c r="E31" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C32" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C33" t="s">
-        <v>27</v>
-      </c>
-      <c r="D33" t="s">
-        <v>55</v>
-      </c>
-      <c r="E33" t="str">
-        <f>'Data LIMIT 1'!$C$1</f>
-        <v>TYPE</v>
       </c>
     </row>
     <row r="34" spans="3:5" x14ac:dyDescent="0.35">
@@ -1244,11 +1601,7 @@
         <v>18</v>
       </c>
       <c r="D34" t="s">
-        <v>61</v>
-      </c>
-      <c r="E34" t="str">
-        <f>'Data LIMIT 1'!$D$1</f>
-        <v>PURPOSE</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="3:5" x14ac:dyDescent="0.35">
@@ -1256,92 +1609,103 @@
         <v>20</v>
       </c>
       <c r="D35" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C36" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="E36" t="str">
+        <f>'Data LIMIT 1'!$C$1</f>
+        <v>TYPE</v>
+      </c>
+    </row>
+    <row r="37" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C37" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" t="s">
+        <v>52</v>
+      </c>
+      <c r="E37" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C38" t="s">
+        <v>25</v>
+      </c>
+      <c r="D38" t="s">
+        <v>50</v>
+      </c>
+      <c r="E38" t="str">
+        <f>'Data LIMIT 1'!$C$1</f>
+        <v>TYPE</v>
+      </c>
+    </row>
+    <row r="39" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C39" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" t="s">
+        <v>56</v>
+      </c>
+      <c r="E39" t="str">
+        <f>'Data LIMIT 1'!$D$1</f>
+        <v>PURPOSE</v>
+      </c>
+    </row>
+    <row r="40" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C41" t="s">
+        <v>25</v>
+      </c>
+      <c r="D41" t="s">
+        <v>58</v>
+      </c>
+      <c r="E41" t="str">
         <f>'Data LIMIT 1'!$E$1</f>
         <v>CLAIM CURRENCY</v>
       </c>
     </row>
-    <row r="37" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C37" t="s">
-        <v>18</v>
-      </c>
-      <c r="D37" t="s">
-        <v>65</v>
-      </c>
-      <c r="E37" t="str">
+    <row r="42" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C42" t="s">
+        <v>16</v>
+      </c>
+      <c r="D42" t="s">
+        <v>60</v>
+      </c>
+      <c r="E42" t="str">
         <f>'Data LIMIT 1'!$F$1</f>
         <v>REFERENCE</v>
       </c>
     </row>
-    <row r="38" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C38" t="s">
-        <v>18</v>
-      </c>
-      <c r="D38" t="s">
-        <v>66</v>
-      </c>
-      <c r="E38" t="str">
+    <row r="43" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C43" t="s">
+        <v>16</v>
+      </c>
+      <c r="D43" t="s">
+        <v>61</v>
+      </c>
+      <c r="E43" t="str">
         <f>'Data LIMIT 1'!$G$1</f>
         <v>DESCRIPTION</v>
       </c>
     </row>
-    <row r="39" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C39" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C40" t="s">
-        <v>20</v>
-      </c>
-      <c r="D40" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="41" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C41" t="s">
-        <v>22</v>
-      </c>
-      <c r="D41" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="42" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C42" t="s">
-        <v>20</v>
-      </c>
-      <c r="D42" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="43" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C43" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43" t="s">
-        <v>70</v>
-      </c>
-    </row>
     <row r="44" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C44" t="s">
-        <v>18</v>
-      </c>
-      <c r="D44" t="s">
-        <v>70</v>
-      </c>
-      <c r="E44" t="str">
-        <f>'Data LIMIT 1'!$H$1</f>
-        <v>FROM DATE CLAIM</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" spans="3:5" x14ac:dyDescent="0.35">
@@ -1349,11 +1713,7 @@
         <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>71</v>
-      </c>
-      <c r="E45" t="str">
-        <f>'Data LIMIT 1'!$I$1</f>
-        <v>TO DATE CLAIM</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="3:5" x14ac:dyDescent="0.35">
@@ -1361,15 +1721,12 @@
         <v>20</v>
       </c>
       <c r="D46" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C47" t="s">
-        <v>22</v>
-      </c>
-      <c r="D47" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="3:5" x14ac:dyDescent="0.35">
@@ -1377,39 +1734,39 @@
         <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>77</v>
-      </c>
-      <c r="E48" t="str">
-        <f>'Data LIMIT 1'!$J$1</f>
-        <v>CLAIM ITEM</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C49" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="D49" t="s">
-        <v>77</v>
-      </c>
-      <c r="E49" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="50" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C50" t="s">
-        <v>54</v>
+        <v>16</v>
+      </c>
+      <c r="D50" t="s">
+        <v>65</v>
+      </c>
+      <c r="E50" t="str">
+        <f>'Data LIMIT 1'!$H$1</f>
+        <v>FROM DATE CLAIM</v>
       </c>
     </row>
     <row r="51" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C51" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D51" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="E51" t="str">
-        <f>'Data LIMIT 1'!$J$1</f>
-        <v>CLAIM ITEM</v>
+        <f>'Data LIMIT 1'!$I$1</f>
+        <v>TO DATE CLAIM</v>
       </c>
     </row>
     <row r="52" spans="3:5" x14ac:dyDescent="0.35">
@@ -1417,115 +1774,118 @@
         <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>79</v>
-      </c>
-      <c r="E52" t="str">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="53" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C53" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C54" t="s">
+        <v>16</v>
+      </c>
+      <c r="D54" t="s">
+        <v>70</v>
+      </c>
+      <c r="E54" t="str">
+        <f>'Data LIMIT 1'!$J$1</f>
+        <v>CLAIM ITEM</v>
+      </c>
+    </row>
+    <row r="55" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C55" t="s">
+        <v>47</v>
+      </c>
+      <c r="D55" t="s">
+        <v>70</v>
+      </c>
+      <c r="E55" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="56" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C56" t="s">
+        <v>25</v>
+      </c>
+      <c r="D56" t="s">
+        <v>50</v>
+      </c>
+      <c r="E56" t="str">
+        <f>'Data LIMIT 1'!$J$1</f>
+        <v>CLAIM ITEM</v>
+      </c>
+    </row>
+    <row r="57" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C57" t="s">
+        <v>16</v>
+      </c>
+      <c r="D57" t="s">
+        <v>72</v>
+      </c>
+      <c r="E57" t="str">
         <f>'Data LIMIT 1'!$K$1</f>
         <v>JUMLAH UNIT</v>
       </c>
     </row>
-    <row r="53" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C53" t="s">
-        <v>18</v>
-      </c>
-      <c r="D53" t="s">
-        <v>80</v>
-      </c>
-      <c r="E53" t="str">
+    <row r="58" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C58" t="s">
+        <v>16</v>
+      </c>
+      <c r="D58" t="s">
+        <v>73</v>
+      </c>
+      <c r="E58" t="str">
         <f>'Data LIMIT 1'!$L$1</f>
         <v>AMOUNT/UNIT</v>
       </c>
     </row>
-    <row r="54" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C54" t="s">
-        <v>18</v>
-      </c>
-      <c r="D54" t="s">
-        <v>81</v>
-      </c>
-      <c r="E54" t="str">
+    <row r="59" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C59" t="s">
+        <v>16</v>
+      </c>
+      <c r="D59" t="s">
+        <v>74</v>
+      </c>
+      <c r="E59" t="str">
         <f>'Data LIMIT 1'!$M$1</f>
         <v>ADJUSTED CLAIM</v>
       </c>
     </row>
-    <row r="55" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C55" t="s">
-        <v>18</v>
-      </c>
-      <c r="D55" t="s">
-        <v>82</v>
-      </c>
-      <c r="E55" t="str">
+    <row r="60" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C60" t="s">
+        <v>16</v>
+      </c>
+      <c r="D60" t="s">
+        <v>75</v>
+      </c>
+      <c r="E60" t="str">
         <f>'Data LIMIT 1'!$N$1</f>
         <v>PROVIDER</v>
       </c>
     </row>
-    <row r="56" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C56" t="s">
-        <v>18</v>
-      </c>
-      <c r="D56" t="s">
-        <v>83</v>
-      </c>
-      <c r="E56" t="str">
+    <row r="61" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C61" t="s">
+        <v>16</v>
+      </c>
+      <c r="D61" t="s">
+        <v>76</v>
+      </c>
+      <c r="E61" t="str">
         <f>'Data LIMIT 1'!$O$1</f>
         <v>DESCRIPTION</v>
       </c>
     </row>
-    <row r="57" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C57" t="s">
-        <v>20</v>
-      </c>
-      <c r="D57" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="58" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C58" t="s">
-        <v>22</v>
-      </c>
-      <c r="D58" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="59" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C59" t="s">
-        <v>18</v>
-      </c>
-      <c r="D59" t="s">
-        <v>89</v>
-      </c>
-      <c r="E59" t="str">
-        <f>'Data LIMIT 1'!$P$1</f>
-        <v>RELATIONSHIP</v>
-      </c>
-    </row>
-    <row r="60" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C60" t="s">
-        <v>52</v>
-      </c>
-      <c r="D60" t="s">
-        <v>89</v>
-      </c>
-      <c r="E60" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="61" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C61" t="s">
-        <v>54</v>
-      </c>
-    </row>
     <row r="62" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C62" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D62" t="s">
-        <v>55</v>
-      </c>
-      <c r="E62" t="str">
-        <f>'Data LIMIT 1'!$P$1</f>
-        <v>RELATIONSHIP</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63" spans="3:5" x14ac:dyDescent="0.35">
@@ -1533,131 +1893,141 @@
         <v>20</v>
       </c>
       <c r="D63" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C64" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D64" t="s">
-        <v>97</v>
+        <v>82</v>
+      </c>
+      <c r="E64" t="str">
+        <f>'Data LIMIT 1'!$P$1</f>
+        <v>RELATIONSHIP</v>
       </c>
     </row>
     <row r="65" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C65" t="s">
+        <v>47</v>
+      </c>
+      <c r="D65" t="s">
+        <v>82</v>
+      </c>
+      <c r="E65" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="66" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C66" t="s">
+        <v>25</v>
+      </c>
+      <c r="D66" t="s">
+        <v>50</v>
+      </c>
+      <c r="E66" t="str">
+        <f>'Data LIMIT 1'!$P$1</f>
+        <v>RELATIONSHIP</v>
+      </c>
+    </row>
+    <row r="67" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C67" t="s">
         <v>18</v>
       </c>
-      <c r="D65" t="s">
-        <v>97</v>
-      </c>
-      <c r="E65" t="str">
+      <c r="D67" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="68" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C68" t="s">
+        <v>20</v>
+      </c>
+      <c r="D68" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="69" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C69" t="s">
+        <v>16</v>
+      </c>
+      <c r="D69" t="s">
+        <v>90</v>
+      </c>
+      <c r="E69" t="str">
         <f>'Data LIMIT 1'!$Q$1</f>
         <v>NAMA RELATIONSHIP</v>
       </c>
     </row>
-    <row r="66" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C66" t="s">
-        <v>52</v>
-      </c>
-      <c r="D66" t="s">
-        <v>97</v>
-      </c>
-      <c r="E66" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="67" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C67" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="68" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C68" t="s">
-        <v>27</v>
-      </c>
-      <c r="D68" t="s">
-        <v>55</v>
-      </c>
-      <c r="E68" t="str">
+    <row r="70" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C70" t="s">
+        <v>47</v>
+      </c>
+      <c r="D70" t="s">
+        <v>90</v>
+      </c>
+      <c r="E70" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="71" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C71" t="s">
+        <v>25</v>
+      </c>
+      <c r="D71" t="s">
+        <v>50</v>
+      </c>
+      <c r="E71" t="str">
         <f>'Data LIMIT 1'!$Q$1</f>
         <v>NAMA RELATIONSHIP</v>
       </c>
     </row>
-    <row r="69" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C69" t="s">
-        <v>18</v>
-      </c>
-      <c r="D69" t="s">
-        <v>98</v>
-      </c>
-      <c r="E69" t="str">
+    <row r="72" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C72" t="s">
+        <v>16</v>
+      </c>
+      <c r="D72" t="s">
+        <v>91</v>
+      </c>
+      <c r="E72" t="str">
         <f>'Data LIMIT 1'!$R$1</f>
         <v>BILL NUMBER</v>
       </c>
     </row>
-    <row r="70" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C70" t="s">
-        <v>18</v>
-      </c>
-      <c r="D70" t="s">
-        <v>99</v>
-      </c>
-      <c r="E70" t="str">
+    <row r="73" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C73" t="s">
+        <v>16</v>
+      </c>
+      <c r="D73" t="s">
+        <v>92</v>
+      </c>
+      <c r="E73" t="str">
         <f>'Data LIMIT 1'!$S$1</f>
         <v>DIAGNOSA</v>
       </c>
     </row>
-    <row r="71" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C71" t="s">
-        <v>20</v>
-      </c>
-      <c r="D71" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="72" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C72" t="s">
-        <v>22</v>
-      </c>
-      <c r="D72" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="73" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C73" t="s">
-        <v>18</v>
-      </c>
-      <c r="D73" t="s">
-        <v>101</v>
-      </c>
-      <c r="E73" t="str">
-        <f>'Data LIMIT 1'!$T$1</f>
-        <v>RS / KLINIK</v>
-      </c>
-    </row>
     <row r="74" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C74" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="D74" t="s">
-        <v>101</v>
-      </c>
-      <c r="E74" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
     </row>
     <row r="75" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C75" t="s">
-        <v>54</v>
+        <v>20</v>
+      </c>
+      <c r="D75" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="76" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C76" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D76" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="E76" t="str">
         <f>'Data LIMIT 1'!$T$1</f>
@@ -1666,27 +2036,369 @@
     </row>
     <row r="77" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C77" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="D77" t="s">
-        <v>102</v>
-      </c>
-      <c r="E77" t="str">
+        <v>94</v>
+      </c>
+      <c r="E77" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="78" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C78" t="s">
+        <v>25</v>
+      </c>
+      <c r="D78" t="s">
+        <v>50</v>
+      </c>
+      <c r="E78" t="str">
+        <f>'Data LIMIT 1'!$T$1</f>
+        <v>RS / KLINIK</v>
+      </c>
+    </row>
+    <row r="79" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C79" t="s">
+        <v>16</v>
+      </c>
+      <c r="D79" t="s">
+        <v>95</v>
+      </c>
+      <c r="E79" t="str">
         <f>'Data LIMIT 1'!$U$1</f>
         <v>RS / KLINIK NAME</v>
       </c>
     </row>
-    <row r="78" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C78" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="79" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C79" t="s">
+    <row r="80" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C80" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="81" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C81" t="s">
+        <v>18</v>
+      </c>
+      <c r="D81" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="82" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C82" t="s">
+        <v>143</v>
+      </c>
+      <c r="D82" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="83" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C83" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C84" t="s">
+        <v>18</v>
+      </c>
+      <c r="D84" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="85" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C85" t="s">
         <v>20</v>
       </c>
-      <c r="D79" t="s">
-        <v>103</v>
+      <c r="D85" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="86" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C86" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="87" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C87" t="s">
+        <v>108</v>
+      </c>
+      <c r="E87" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="88" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C88" t="s">
+        <v>18</v>
+      </c>
+      <c r="D88" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="89" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C89" t="s">
+        <v>20</v>
+      </c>
+      <c r="D89" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="90" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C90" t="s">
+        <v>16</v>
+      </c>
+      <c r="D90" t="s">
+        <v>120</v>
+      </c>
+      <c r="E90" t="str">
+        <f>Data_Attachment!$B$1</f>
+        <v>DOCUMENT NUMBER</v>
+      </c>
+    </row>
+    <row r="91" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C91" t="s">
+        <v>18</v>
+      </c>
+      <c r="D91" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="92" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C92" t="s">
+        <v>20</v>
+      </c>
+      <c r="D92" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="93" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C93" t="s">
+        <v>16</v>
+      </c>
+      <c r="D93" t="s">
+        <v>107</v>
+      </c>
+      <c r="E93" t="str">
+        <f>Data_Attachment!$C$1</f>
+        <v>DOCUMENT TYPE</v>
+      </c>
+    </row>
+    <row r="94" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C94" t="s">
+        <v>47</v>
+      </c>
+      <c r="D94" t="s">
+        <v>107</v>
+      </c>
+      <c r="E94" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="95" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C95" t="s">
+        <v>25</v>
+      </c>
+      <c r="D95" t="s">
+        <v>50</v>
+      </c>
+      <c r="E95" t="str">
+        <f>Data_Attachment!$C$1</f>
+        <v>DOCUMENT TYPE</v>
+      </c>
+    </row>
+    <row r="96" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C96" t="s">
+        <v>16</v>
+      </c>
+      <c r="D96" t="s">
+        <v>131</v>
+      </c>
+      <c r="E96" t="str">
+        <f>Data_Attachment!$D$1</f>
+        <v>DOCUMENT EXPIRED DATE</v>
+      </c>
+    </row>
+    <row r="97" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C97" t="s">
+        <v>16</v>
+      </c>
+      <c r="D97" t="s">
+        <v>132</v>
+      </c>
+      <c r="E97" t="str">
+        <f>Data_Attachment!$E$1</f>
+        <v>DESCRIPTION</v>
+      </c>
+    </row>
+    <row r="98" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C98" t="s">
+        <v>16</v>
+      </c>
+      <c r="D98" t="s">
+        <v>133</v>
+      </c>
+      <c r="E98" t="str">
+        <f>Data_Attachment!$F$1</f>
+        <v>ISSUED DATE</v>
+      </c>
+    </row>
+    <row r="99" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C99" t="s">
+        <v>16</v>
+      </c>
+      <c r="D99" t="s">
+        <v>134</v>
+      </c>
+      <c r="E99" t="str">
+        <f>Data_Attachment!$G$1</f>
+        <v>ISSUED BY</v>
+      </c>
+    </row>
+    <row r="100" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C100" t="s">
+        <v>136</v>
+      </c>
+      <c r="D100" t="s">
+        <v>135</v>
+      </c>
+      <c r="E100" t="str">
+        <f>Data_Attachment!$H$1</f>
+        <v>FILE PATH ATTACH</v>
+      </c>
+    </row>
+    <row r="101" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C101" t="s">
+        <v>18</v>
+      </c>
+      <c r="D101" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="102" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C102" t="s">
+        <v>20</v>
+      </c>
+      <c r="D102" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="103" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C103" t="s">
+        <v>110</v>
+      </c>
+      <c r="E103" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="104" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C104" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="105" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C105" t="s">
+        <v>18</v>
+      </c>
+      <c r="D105" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="106" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C106" t="s">
+        <v>18</v>
+      </c>
+      <c r="D106" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="107" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C107" t="s">
+        <v>20</v>
+      </c>
+      <c r="D107" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="108" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C108" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="109" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C109" t="s">
+        <v>18</v>
+      </c>
+      <c r="D109" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="110" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C110" t="s">
+        <v>143</v>
+      </c>
+      <c r="D110" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="111" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C111" t="s">
+        <v>20</v>
+      </c>
+      <c r="D111" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="112" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C112" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C113" s="4"/>
+      <c r="D113" s="4"/>
+      <c r="E113" s="4"/>
+      <c r="F113" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C114" t="s">
+        <v>18</v>
+      </c>
+      <c r="D114" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C115" t="s">
+        <v>18</v>
+      </c>
+      <c r="D115" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C116" t="s">
+        <v>18</v>
+      </c>
+      <c r="D116" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C117" t="s">
+        <v>20</v>
+      </c>
+      <c r="D117" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C118" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1726,64 +2438,64 @@
         <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="J1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="U1" s="2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.35">
@@ -1791,56 +2503,56 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="G2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="J2" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="K2" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="R2" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="S2" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="T2" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="U2" s="8"/>
+      <c r="H2" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="T2" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="U2" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1848,13 +2560,133 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05D10CBA-C190-428F-999E-70591B80DCCA}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="3.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6328125" customWidth="1"/>
+    <col min="8" max="8" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="E4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G4" t="s">
+        <v>119</v>
+      </c>
+      <c r="H4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="116.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -1862,7 +2694,495 @@
         <v>6</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>91</v>
+      </c>
+      <c r="B36" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>92</v>
+      </c>
+      <c r="B37" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>93</v>
+      </c>
+      <c r="B38" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>94</v>
+      </c>
+      <c r="B39" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>95</v>
+      </c>
+      <c r="B40" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>105</v>
+      </c>
+      <c r="B42" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>106</v>
+      </c>
+      <c r="B43" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>120</v>
+      </c>
+      <c r="B44" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>121</v>
+      </c>
+      <c r="B45" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>107</v>
+      </c>
+      <c r="B46" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>131</v>
+      </c>
+      <c r="B47" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>132</v>
+      </c>
+      <c r="B48" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>133</v>
+      </c>
+      <c r="B49" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>134</v>
+      </c>
+      <c r="B50" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>135</v>
+      </c>
+      <c r="B51" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>137</v>
+      </c>
+      <c r="B52" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>138</v>
+      </c>
+      <c r="B53" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>139</v>
+      </c>
+      <c r="B54" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>140</v>
+      </c>
+      <c r="B55" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>141</v>
+      </c>
+      <c r="B56" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>152</v>
+      </c>
+      <c r="B57" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>142</v>
+      </c>
+      <c r="B58" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>144</v>
+      </c>
+      <c r="B59" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>148</v>
+      </c>
+      <c r="B60" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>211</v>
+      </c>
+      <c r="B61" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>216</v>
+      </c>
+      <c r="B62" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/BTNBest - Claim Benefit.xlsx
+++ b/src/main/resources/BTNBest - Claim Benefit.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KERJA\Intellij Project\Testing\Testing\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E2E501-4C78-412C-94DD-1A1BEDA2D26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{056519B8-7B77-4AD4-8E14-86D06189870A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA-INFO" sheetId="1" r:id="rId1"/>
-    <sheet name="Datatable" sheetId="2" r:id="rId2"/>
-    <sheet name="dt_Initial Data Entry" sheetId="6" state="hidden" r:id="rId3"/>
+    <sheet name="dt_Initial Data Entry" sheetId="6" state="hidden" r:id="rId2"/>
+    <sheet name="Datatable" sheetId="2" r:id="rId3"/>
     <sheet name="LIMIT 1" sheetId="4" r:id="rId4"/>
     <sheet name="Data LIMIT 1" sheetId="9" r:id="rId5"/>
     <sheet name="Data_Attachment" sheetId="10" r:id="rId6"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="226">
   <si>
     <t>Start Data</t>
   </si>
@@ -140,9 +140,6 @@
     <t>BTNBEST</t>
   </si>
   <si>
-    <t>https://btn-uat.harpa-go.com:9443/login</t>
-  </si>
-  <si>
     <t>Claim Benefit Pusat Limit 1</t>
   </si>
   <si>
@@ -401,9 +398,6 @@
     <t>FILE PATH ATTACH</t>
   </si>
   <si>
-    <t>ODY</t>
-  </si>
-  <si>
     <t>txtDocumentNumber</t>
   </si>
   <si>
@@ -503,9 +497,6 @@
     <t>btnOKPopUp</t>
   </si>
   <si>
-    <t>C:\\KERJA\\UAT Script.docx</t>
-  </si>
-  <si>
     <t>//input[@name='user_name']</t>
   </si>
   <si>
@@ -707,21 +698,12 @@
     <t>start_new_driver</t>
   </si>
   <si>
-    <t>DIDIT10131@TEST.COM</t>
-  </si>
-  <si>
-    <t>Btnbest321#</t>
-  </si>
-  <si>
     <t>Gigi</t>
   </si>
   <si>
     <t>Claim Gigi</t>
   </si>
   <si>
-    <t>DIDIT NURYANTO</t>
-  </si>
-  <si>
     <t>SIT</t>
   </si>
   <si>
@@ -735,6 +717,9 @@
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>DIDIT</t>
   </si>
 </sst>
 </file>
@@ -805,27 +790,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -842,10 +812,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1155,7 +1125,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -1165,6 +1135,41 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35BD06DC-ED1D-4738-A7E0-2CC2298E6BD6}">
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="14.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:J9"/>
@@ -1194,13 +1199,13 @@
         <v>9</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>21</v>
@@ -1217,19 +1222,13 @@
         <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>222</v>
-      </c>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="11"/>
       <c r="G2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
@@ -1237,44 +1236,6 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="J9" t="s">
         <v>22</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{7DCF6C9C-BC1D-4199-A786-F1BEDEFD0845}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35BD06DC-ED1D-4738-A7E0-2CC2298E6BD6}">
-  <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="14.90625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1293,7 +1254,7 @@
     <col min="3" max="3" width="25.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.90625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="31.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.81640625" style="11" customWidth="1"/>
+    <col min="6" max="6" width="15.81640625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.35">
@@ -1332,7 +1293,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -1349,7 +1310,7 @@
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -1362,7 +1323,7 @@
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E7" t="str">
         <f>Datatable!$E$1</f>
@@ -1399,23 +1360,23 @@
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C13" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D13" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -1424,11 +1385,11 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="10" t="s">
-        <v>37</v>
+      <c r="A15" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -1442,7 +1403,7 @@
         <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.35">
@@ -1450,7 +1411,7 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E17" t="str">
         <f>Datatable!$G$1</f>
@@ -1459,32 +1420,32 @@
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" t="s">
+        <v>140</v>
+      </c>
+      <c r="E18" t="s">
         <v>47</v>
-      </c>
-      <c r="D18" t="s">
-        <v>142</v>
-      </c>
-      <c r="E18" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C19" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D19" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C20" t="s">
+        <v>145</v>
+      </c>
+      <c r="D20" t="s">
+        <v>146</v>
+      </c>
+      <c r="E20" t="s">
         <v>147</v>
-      </c>
-      <c r="D20" t="s">
-        <v>148</v>
-      </c>
-      <c r="E20" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="21" spans="3:5" x14ac:dyDescent="0.35">
@@ -1492,15 +1453,15 @@
         <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C22" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E22" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" spans="3:5" x14ac:dyDescent="0.35">
@@ -1508,7 +1469,7 @@
         <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="3:5" x14ac:dyDescent="0.35">
@@ -1516,7 +1477,7 @@
         <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="3:5" x14ac:dyDescent="0.35">
@@ -1529,7 +1490,7 @@
         <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="3:5" x14ac:dyDescent="0.35">
@@ -1537,7 +1498,7 @@
         <v>20</v>
       </c>
       <c r="D27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="3:5" x14ac:dyDescent="0.35">
@@ -1550,7 +1511,7 @@
         <v>18</v>
       </c>
       <c r="D29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="3:5" x14ac:dyDescent="0.35">
@@ -1558,7 +1519,7 @@
         <v>20</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="3:5" x14ac:dyDescent="0.35">
@@ -1566,7 +1527,7 @@
         <v>16</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E31" t="str">
         <f>'Data LIMIT 1'!$B$1</f>
@@ -1575,13 +1536,13 @@
     </row>
     <row r="32" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C32" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" t="s">
         <v>47</v>
-      </c>
-      <c r="D32" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="33" spans="3:5" x14ac:dyDescent="0.35">
@@ -1589,7 +1550,7 @@
         <v>25</v>
       </c>
       <c r="D33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E33" t="str">
         <f>'Data LIMIT 1'!$B$1</f>
@@ -1601,7 +1562,7 @@
         <v>18</v>
       </c>
       <c r="D34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="3:5" x14ac:dyDescent="0.35">
@@ -1609,7 +1570,7 @@
         <v>20</v>
       </c>
       <c r="D35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="3:5" x14ac:dyDescent="0.35">
@@ -1617,7 +1578,7 @@
         <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E36" t="str">
         <f>'Data LIMIT 1'!$C$1</f>
@@ -1626,13 +1587,13 @@
     </row>
     <row r="37" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C37" t="s">
+        <v>46</v>
+      </c>
+      <c r="D37" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" t="s">
         <v>47</v>
-      </c>
-      <c r="D37" t="s">
-        <v>52</v>
-      </c>
-      <c r="E37" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="38" spans="3:5" x14ac:dyDescent="0.35">
@@ -1640,7 +1601,7 @@
         <v>25</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E38" t="str">
         <f>'Data LIMIT 1'!$C$1</f>
@@ -1652,7 +1613,7 @@
         <v>16</v>
       </c>
       <c r="D39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E39" t="str">
         <f>'Data LIMIT 1'!$D$1</f>
@@ -1664,7 +1625,7 @@
         <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41" spans="3:5" x14ac:dyDescent="0.35">
@@ -1672,7 +1633,7 @@
         <v>25</v>
       </c>
       <c r="D41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E41" t="str">
         <f>'Data LIMIT 1'!$E$1</f>
@@ -1684,7 +1645,7 @@
         <v>16</v>
       </c>
       <c r="D42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E42" t="str">
         <f>'Data LIMIT 1'!$F$1</f>
@@ -1696,7 +1657,7 @@
         <v>16</v>
       </c>
       <c r="D43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E43" t="str">
         <f>'Data LIMIT 1'!$G$1</f>
@@ -1705,7 +1666,7 @@
     </row>
     <row r="44" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="3:5" x14ac:dyDescent="0.35">
@@ -1713,7 +1674,7 @@
         <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="3:5" x14ac:dyDescent="0.35">
@@ -1721,12 +1682,12 @@
         <v>20</v>
       </c>
       <c r="D46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="48" spans="3:5" x14ac:dyDescent="0.35">
@@ -1734,7 +1695,7 @@
         <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49" spans="3:5" x14ac:dyDescent="0.35">
@@ -1742,7 +1703,7 @@
         <v>20</v>
       </c>
       <c r="D49" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="50" spans="3:5" x14ac:dyDescent="0.35">
@@ -1750,7 +1711,7 @@
         <v>16</v>
       </c>
       <c r="D50" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E50" t="str">
         <f>'Data LIMIT 1'!$H$1</f>
@@ -1762,7 +1723,7 @@
         <v>16</v>
       </c>
       <c r="D51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E51" t="str">
         <f>'Data LIMIT 1'!$I$1</f>
@@ -1774,7 +1735,7 @@
         <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="3:5" x14ac:dyDescent="0.35">
@@ -1782,7 +1743,7 @@
         <v>20</v>
       </c>
       <c r="D53" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54" spans="3:5" x14ac:dyDescent="0.35">
@@ -1790,7 +1751,7 @@
         <v>16</v>
       </c>
       <c r="D54" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E54" t="str">
         <f>'Data LIMIT 1'!$J$1</f>
@@ -1799,13 +1760,13 @@
     </row>
     <row r="55" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C55" t="s">
+        <v>46</v>
+      </c>
+      <c r="D55" t="s">
+        <v>69</v>
+      </c>
+      <c r="E55" t="s">
         <v>47</v>
-      </c>
-      <c r="D55" t="s">
-        <v>70</v>
-      </c>
-      <c r="E55" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="56" spans="3:5" x14ac:dyDescent="0.35">
@@ -1813,7 +1774,7 @@
         <v>25</v>
       </c>
       <c r="D56" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E56" t="str">
         <f>'Data LIMIT 1'!$J$1</f>
@@ -1825,7 +1786,7 @@
         <v>16</v>
       </c>
       <c r="D57" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E57" t="str">
         <f>'Data LIMIT 1'!$K$1</f>
@@ -1837,7 +1798,7 @@
         <v>16</v>
       </c>
       <c r="D58" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E58" t="str">
         <f>'Data LIMIT 1'!$L$1</f>
@@ -1849,7 +1810,7 @@
         <v>16</v>
       </c>
       <c r="D59" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E59" t="str">
         <f>'Data LIMIT 1'!$M$1</f>
@@ -1861,7 +1822,7 @@
         <v>16</v>
       </c>
       <c r="D60" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E60" t="str">
         <f>'Data LIMIT 1'!$N$1</f>
@@ -1873,7 +1834,7 @@
         <v>16</v>
       </c>
       <c r="D61" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E61" t="str">
         <f>'Data LIMIT 1'!$O$1</f>
@@ -1885,7 +1846,7 @@
         <v>18</v>
       </c>
       <c r="D62" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" spans="3:5" x14ac:dyDescent="0.35">
@@ -1893,7 +1854,7 @@
         <v>20</v>
       </c>
       <c r="D63" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="64" spans="3:5" x14ac:dyDescent="0.35">
@@ -1901,7 +1862,7 @@
         <v>16</v>
       </c>
       <c r="D64" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E64" t="str">
         <f>'Data LIMIT 1'!$P$1</f>
@@ -1910,13 +1871,13 @@
     </row>
     <row r="65" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C65" t="s">
+        <v>46</v>
+      </c>
+      <c r="D65" t="s">
+        <v>81</v>
+      </c>
+      <c r="E65" t="s">
         <v>47</v>
-      </c>
-      <c r="D65" t="s">
-        <v>82</v>
-      </c>
-      <c r="E65" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="66" spans="3:5" x14ac:dyDescent="0.35">
@@ -1924,7 +1885,7 @@
         <v>25</v>
       </c>
       <c r="D66" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E66" t="str">
         <f>'Data LIMIT 1'!$P$1</f>
@@ -1936,7 +1897,7 @@
         <v>18</v>
       </c>
       <c r="D67" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="3:5" x14ac:dyDescent="0.35">
@@ -1944,7 +1905,7 @@
         <v>20</v>
       </c>
       <c r="D68" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69" spans="3:5" x14ac:dyDescent="0.35">
@@ -1952,7 +1913,7 @@
         <v>16</v>
       </c>
       <c r="D69" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E69" t="str">
         <f>'Data LIMIT 1'!$Q$1</f>
@@ -1961,13 +1922,13 @@
     </row>
     <row r="70" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C70" t="s">
+        <v>46</v>
+      </c>
+      <c r="D70" t="s">
+        <v>89</v>
+      </c>
+      <c r="E70" t="s">
         <v>47</v>
-      </c>
-      <c r="D70" t="s">
-        <v>90</v>
-      </c>
-      <c r="E70" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="71" spans="3:5" x14ac:dyDescent="0.35">
@@ -1975,7 +1936,7 @@
         <v>25</v>
       </c>
       <c r="D71" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E71" t="str">
         <f>'Data LIMIT 1'!$Q$1</f>
@@ -1987,7 +1948,7 @@
         <v>16</v>
       </c>
       <c r="D72" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E72" t="str">
         <f>'Data LIMIT 1'!$R$1</f>
@@ -1999,7 +1960,7 @@
         <v>16</v>
       </c>
       <c r="D73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E73" t="str">
         <f>'Data LIMIT 1'!$S$1</f>
@@ -2011,7 +1972,7 @@
         <v>18</v>
       </c>
       <c r="D74" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="75" spans="3:5" x14ac:dyDescent="0.35">
@@ -2019,7 +1980,7 @@
         <v>20</v>
       </c>
       <c r="D75" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="76" spans="3:5" x14ac:dyDescent="0.35">
@@ -2027,7 +1988,7 @@
         <v>16</v>
       </c>
       <c r="D76" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E76" t="str">
         <f>'Data LIMIT 1'!$T$1</f>
@@ -2036,13 +1997,13 @@
     </row>
     <row r="77" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C77" t="s">
+        <v>46</v>
+      </c>
+      <c r="D77" t="s">
+        <v>93</v>
+      </c>
+      <c r="E77" t="s">
         <v>47</v>
-      </c>
-      <c r="D77" t="s">
-        <v>94</v>
-      </c>
-      <c r="E77" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="78" spans="3:5" x14ac:dyDescent="0.35">
@@ -2050,7 +2011,7 @@
         <v>25</v>
       </c>
       <c r="D78" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E78" t="str">
         <f>'Data LIMIT 1'!$T$1</f>
@@ -2062,7 +2023,7 @@
         <v>16</v>
       </c>
       <c r="D79" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E79" t="str">
         <f>'Data LIMIT 1'!$U$1</f>
@@ -2071,7 +2032,7 @@
     </row>
     <row r="80" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C80" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="81" spans="3:5" x14ac:dyDescent="0.35">
@@ -2079,15 +2040,15 @@
         <v>18</v>
       </c>
       <c r="D81" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="82" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C82" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D82" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="83" spans="3:5" x14ac:dyDescent="0.35">
@@ -2100,7 +2061,7 @@
         <v>18</v>
       </c>
       <c r="D84" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="85" spans="3:5" x14ac:dyDescent="0.35">
@@ -2108,20 +2069,20 @@
         <v>20</v>
       </c>
       <c r="D85" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="86" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C86" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="87" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C87" t="s">
+        <v>107</v>
+      </c>
+      <c r="E87" t="s">
         <v>108</v>
-      </c>
-      <c r="E87" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="88" spans="3:5" x14ac:dyDescent="0.35">
@@ -2129,7 +2090,7 @@
         <v>18</v>
       </c>
       <c r="D88" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="89" spans="3:5" x14ac:dyDescent="0.35">
@@ -2137,7 +2098,7 @@
         <v>20</v>
       </c>
       <c r="D89" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="90" spans="3:5" x14ac:dyDescent="0.35">
@@ -2145,7 +2106,7 @@
         <v>16</v>
       </c>
       <c r="D90" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E90" t="str">
         <f>Data_Attachment!$B$1</f>
@@ -2157,7 +2118,7 @@
         <v>18</v>
       </c>
       <c r="D91" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="92" spans="3:5" x14ac:dyDescent="0.35">
@@ -2165,7 +2126,7 @@
         <v>20</v>
       </c>
       <c r="D92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="93" spans="3:5" x14ac:dyDescent="0.35">
@@ -2173,7 +2134,7 @@
         <v>16</v>
       </c>
       <c r="D93" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E93" t="str">
         <f>Data_Attachment!$C$1</f>
@@ -2182,13 +2143,13 @@
     </row>
     <row r="94" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C94" t="s">
+        <v>46</v>
+      </c>
+      <c r="D94" t="s">
+        <v>106</v>
+      </c>
+      <c r="E94" t="s">
         <v>47</v>
-      </c>
-      <c r="D94" t="s">
-        <v>107</v>
-      </c>
-      <c r="E94" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="95" spans="3:5" x14ac:dyDescent="0.35">
@@ -2196,7 +2157,7 @@
         <v>25</v>
       </c>
       <c r="D95" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E95" t="str">
         <f>Data_Attachment!$C$1</f>
@@ -2208,7 +2169,7 @@
         <v>16</v>
       </c>
       <c r="D96" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E96" t="str">
         <f>Data_Attachment!$D$1</f>
@@ -2220,7 +2181,7 @@
         <v>16</v>
       </c>
       <c r="D97" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E97" t="str">
         <f>Data_Attachment!$E$1</f>
@@ -2232,7 +2193,7 @@
         <v>16</v>
       </c>
       <c r="D98" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E98" t="str">
         <f>Data_Attachment!$F$1</f>
@@ -2244,7 +2205,7 @@
         <v>16</v>
       </c>
       <c r="D99" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E99" t="str">
         <f>Data_Attachment!$G$1</f>
@@ -2253,10 +2214,10 @@
     </row>
     <row r="100" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C100" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D100" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E100" t="str">
         <f>Data_Attachment!$H$1</f>
@@ -2268,7 +2229,7 @@
         <v>18</v>
       </c>
       <c r="D101" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="102" spans="3:5" x14ac:dyDescent="0.35">
@@ -2276,20 +2237,20 @@
         <v>20</v>
       </c>
       <c r="D102" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="103" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C103" t="s">
+        <v>109</v>
+      </c>
+      <c r="E103" t="s">
         <v>110</v>
-      </c>
-      <c r="E103" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="104" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C104" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="105" spans="3:5" x14ac:dyDescent="0.35">
@@ -2297,7 +2258,7 @@
         <v>18</v>
       </c>
       <c r="D105" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="106" spans="3:5" x14ac:dyDescent="0.35">
@@ -2305,7 +2266,7 @@
         <v>18</v>
       </c>
       <c r="D106" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="107" spans="3:5" x14ac:dyDescent="0.35">
@@ -2313,12 +2274,12 @@
         <v>20</v>
       </c>
       <c r="D107" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="108" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C108" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="109" spans="3:5" x14ac:dyDescent="0.35">
@@ -2326,15 +2287,15 @@
         <v>18</v>
       </c>
       <c r="D109" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="110" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C110" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D110" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="111" spans="3:5" x14ac:dyDescent="0.35">
@@ -2342,20 +2303,20 @@
         <v>20</v>
       </c>
       <c r="D111" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="112" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C112" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A113" s="10" t="s">
-        <v>213</v>
+      <c r="A113" s="8" t="s">
+        <v>210</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C113" s="4"/>
       <c r="D113" s="4"/>
@@ -2369,7 +2330,7 @@
         <v>18</v>
       </c>
       <c r="D114" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
@@ -2377,7 +2338,7 @@
         <v>18</v>
       </c>
       <c r="D115" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
@@ -2385,7 +2346,7 @@
         <v>18</v>
       </c>
       <c r="D116" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
@@ -2398,7 +2359,7 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C118" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2438,64 +2399,64 @@
         <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="H1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="J1" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="O1" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.35">
@@ -2503,54 +2464,54 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2" t="s">
         <v>102</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>103</v>
       </c>
-      <c r="G2" t="s">
-        <v>104</v>
-      </c>
       <c r="H2" s="7" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="J2" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L2" s="7" t="s">
         <v>223</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>229</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="7"/>
       <c r="O2" s="7" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="P2" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q2" s="7" t="s">
         <v>225</v>
       </c>
       <c r="R2" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="S2" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="S2" s="7" t="s">
+      <c r="T2" s="7" t="s">
         <v>100</v>
-      </c>
-      <c r="T2" s="7" t="s">
-        <v>101</v>
       </c>
       <c r="U2" s="7"/>
     </row>
@@ -2580,25 +2541,25 @@
         <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>116</v>
-      </c>
       <c r="H1" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -2606,22 +2567,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="G2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H2" t="s">
-        <v>153</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -2629,22 +2584,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="G3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H3" t="s">
-        <v>153</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -2652,25 +2601,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="G4" t="s">
-        <v>119</v>
-      </c>
-      <c r="H4" t="s">
-        <v>153</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -2699,10 +2642,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -2710,15 +2653,15 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -2726,463 +2669,463 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B8" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B17" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B18" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B19" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B24" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B25" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B26" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B27" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B28" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B29" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B30" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B31" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B32" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B33" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B34" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B35" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B36" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B37" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B38" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B39" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B40" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B41" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B42" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B43" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B44" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B45" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B46" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B47" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B48" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B49" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B50" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B51" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B52" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B53" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B54" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B55" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B56" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B57" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B58" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B59" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B60" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B61" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B62" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
